--- a/naver-place-crawler/results_health/하남_PT.xlsx
+++ b/naver-place-crawler/results_health/하남_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>에이블짐 미사역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>ablegym43@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>0507-1469-2444</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기도 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://blog.naver.com/ablegym43</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>879</v>
+        <v>1488</v>
       </c>
       <c r="Q2" t="n">
-        <v>2011</v>
+        <v>1337</v>
       </c>
       <c r="R2" t="n">
-        <v>2890</v>
+        <v>2825</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,47 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>2037860861</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/2037860861</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>레이크짐 PT 미사점</t>
+          <t>짐맥스 미사역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lakegym@naver.com</t>
+          <t>gymax_01@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1469-4114</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
+          <t>경기도 하남시 미사강변동로84번길 21 남송타워 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lakegym</t>
+          <t>https://blog.naver.com/gymax_01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>288</v>
+        <v>3332</v>
       </c>
       <c r="Q3" t="n">
-        <v>501</v>
+        <v>643</v>
       </c>
       <c r="R3" t="n">
-        <v>789</v>
+        <v>3975</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +726,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1857191169</t>
+          <t>1328828814</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857191169</t>
+          <t>https://m.place.naver.com/place/1328828814</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용 헬스 PT 레이디짐 미사점</t>
+          <t>샤인휘트니스 미사역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitgirl24@naver.com</t>
+          <t>shine_fitness4@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1345-3449</t>
+          <t>0507-1429-6523</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
+          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitgirl24</t>
+          <t>https://blog.naver.com/shine_fitness4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>499</v>
+        <v>898</v>
       </c>
       <c r="Q4" t="n">
-        <v>597</v>
+        <v>2015</v>
       </c>
       <c r="R4" t="n">
-        <v>1096</v>
+        <v>2913</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +820,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1945229916</t>
+          <t>1377711586</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945229916</t>
+          <t>https://m.place.naver.com/place/1377711586</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>뉴짐스PT&amp;크루</t>
+          <t>여성전용 헬스 PT 레이디짐 미사점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>woongchan_pt@naver.com</t>
+          <t>fitgirl24@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1342-3414</t>
+          <t>0507-1345-3449</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
+          <t>경기도 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woongchan_pt</t>
+          <t>https://blog.naver.com/fitgirl24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>136</v>
+        <v>498</v>
       </c>
       <c r="Q5" t="n">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="R5" t="n">
-        <v>760</v>
+        <v>1110</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +914,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1577544321</t>
+          <t>1945229916</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577544321</t>
+          <t>https://m.place.naver.com/place/1945229916</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더하남 그룹PT 키네틱캠프 미사점</t>
+          <t>레이크짐 PT 미사점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mvppvm@naver.com</t>
+          <t>lakegym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1387-4464</t>
+          <t>0507-1469-4114</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mvppvm/222632646985</t>
+          <t>https://www.instagram.com/lakegym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>757</v>
+        <v>287</v>
       </c>
       <c r="Q6" t="n">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="R6" t="n">
-        <v>1082</v>
+        <v>787</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1008,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1949849359</t>
+          <t>1857191169</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949849359</t>
+          <t>https://m.place.naver.com/place/1857191169</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여성전용 그룹PT 엑서트 위례점</t>
+          <t>뉴짐스PT&amp;크루</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>exert_701@naver.com</t>
+          <t>woongchan_pt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-2755</t>
+          <t>0507-1342-3414</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 하남시 위례학암로14번길 31 경서타워2 7층</t>
+          <t>경기도 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JQgan</t>
+          <t>https://blog.naver.com/woongchan_pt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="Q7" t="n">
-        <v>267</v>
+        <v>614</v>
       </c>
       <c r="R7" t="n">
-        <v>291</v>
+        <v>751</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2027288661</t>
+          <t>1577544321</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2027288661</t>
+          <t>https://m.place.naver.com/place/1577544321</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>카인드짐24시 헬스 PT 미사역점</t>
+          <t>더하남 그룹PT 키네틱캠프 미사점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kindgym8@naver.com</t>
+          <t>mvppvm@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1459-2444</t>
+          <t>0507-1387-4464</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변남로 125 미사역 마이움푸르지오시티 B1</t>
+          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_zxeEXK</t>
+          <t>https://blog.naver.com/mvppvm/222632646985</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1148</v>
+        <v>758</v>
       </c>
       <c r="Q8" t="n">
-        <v>1298</v>
+        <v>327</v>
       </c>
       <c r="R8" t="n">
-        <v>2446</v>
+        <v>1085</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1845162608</t>
+          <t>1949849359</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845162608</t>
+          <t>https://m.place.naver.com/place/1949849359</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>포시즌휘트니스&amp;골프 하남미사점</t>
+          <t>86피트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fseason792@naver.com</t>
+          <t>86fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-1636</t>
+          <t>0507-1300-6180</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로 73 노블레스타워 11층</t>
+          <t>경기도 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fseason792</t>
+          <t>https://cafe.naver.com/jetleezumba/28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>751</v>
+        <v>431</v>
       </c>
       <c r="Q9" t="n">
-        <v>1182</v>
+        <v>234</v>
       </c>
       <c r="R9" t="n">
-        <v>1933</v>
+        <v>665</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>624955172</t>
+          <t>1987758688</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/624955172</t>
+          <t>https://m.place.naver.com/place/1987758688</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>86피트니스</t>
+          <t>에이투에프 하남</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>86fitness@naver.com</t>
+          <t>a2f_online@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1300-6180</t>
+          <t>0507-1381-5791</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
+          <t>경기 하남시 대성로319번길 50 한림빌딩 B1호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jetleezumba/28</t>
+          <t>https://blog.naver.com/a2f_online</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1354,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wo29jot</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="n">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="R10" t="n">
-        <v>683</v>
+        <v>322</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1987758688</t>
+          <t>1744117426</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987758688</t>
+          <t>https://m.place.naver.com/place/1744117426</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>프롬더스트릿 하남미사점</t>
+          <t>에어바이트 PT 미사점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fromthestreet@naver.com</t>
+          <t>airbite@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1369-1637</t>
+          <t>0507-1332-4181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 189 307호</t>
+          <t>경기도 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Fromthestreet</t>
+          <t>https://www.instagram.com/_ko_coach</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="Q11" t="n">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>473</v>
+        <v>103</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,957 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1280710452</t>
+          <t>2000579553</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280710452</t>
+          <t>https://m.place.naver.com/place/2000579553</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>그로우걸 여성전용 그룹PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>growgirl_fit@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1343-0367</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 하남시 신평로 49 6층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/growgirl_fit</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>70</v>
-      </c>
-      <c r="R12" t="n">
-        <v>77</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2003214630</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2003214630</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>아인스휘트니스 헬스 PT 골프 GX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>einsfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1344-8363</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 하남시 신장로 151 대동피렌체 지하1층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/e1nsfitness?igsh=M3R5dnU5MWYxamR0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>563</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>505</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1068</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>468234581</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/468234581</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>아이엠피티</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>iampt0411@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1422-0411</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 하남시 미사강변중앙로170번길 10 401호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/iampt0411</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>366</v>
-      </c>
-      <c r="R14" t="n">
-        <v>454</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1817320671</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1817320671</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>포데이짐PT 하남미사점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>fourdaygym@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1347-3173</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 하남시 미사강변동로 81 5층 502호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fourdaygym</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>236</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>450</v>
-      </c>
-      <c r="R15" t="n">
-        <v>686</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1167442751</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1167442751</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>위드짐PT 하남미사</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>withgym01@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1300-1929</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 하남시 미사강변대로 84 305, 306호</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/withgym01</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>113</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>323</v>
-      </c>
-      <c r="R16" t="n">
-        <v>436</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1010268294</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1010268294</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>에그짐 미사역점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>eggym-misa@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1416-9050</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 하남시 미사강변중앙로204번길 22 3층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>http://www.eggym.co.kr</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>397</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1199</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1596</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1244434346</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1244434346</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>웰컴피트니스 풍산점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>welcomefit@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1485-7234</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 하남시 덕풍동로 111 9층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/welcome__fit</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>65</v>
-      </c>
-      <c r="R18" t="n">
-        <v>161</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2076027825</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2076027825</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>jw30-lim@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1345-9570</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 하남시 미사강변중앙로 165 신성프라자2 2층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/jw30-lim</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>109</v>
-      </c>
-      <c r="R19" t="n">
-        <v>194</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1350773756</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>아벨짐PT 하남미사점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>romangfit_@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1432-1803</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 하남시 미사강변남로 87 스타파크 2층 203호, 212호</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/romangfit_</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>534</v>
-      </c>
-      <c r="R20" t="n">
-        <v>687</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1383123287</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1383123287</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>그로우짐 PT&amp;헬스 하남시청점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>thehanam_grow24@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>070-4149-0366</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 하남시 신평로 49 B1층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/thehanam_grow24</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>275</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>329</v>
-      </c>
-      <c r="R21" t="n">
-        <v>604</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1151553186</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1151553186</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/하남_PT.xlsx
+++ b/naver-place-crawler/results_health/하남_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
+          <t>경기도 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5rxl0a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="Q2" t="n">
         <v>1337</v>
       </c>
       <c r="R2" t="n">
-        <v>2829</v>
+        <v>2831</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +671,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
+          <t>경기도 하남시 미사강변동로84번길 21 남송타워 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +696,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wr0uh6r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3351</v>
+        <v>3354</v>
       </c>
       <c r="Q3" t="n">
         <v>654</v>
       </c>
       <c r="R3" t="n">
-        <v>4005</v>
+        <v>4008</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -773,7 +765,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,14 +790,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1sjoqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -871,7 +859,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +884,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48112</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -969,7 +953,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
+          <t>경기도 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +978,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44bi7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1050,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레이크짐 PT 미사점</t>
+          <t>뉴짐스PT&amp;크루</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lakegym@naver.com</t>
+          <t>woongchan_pt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1469-4114</t>
+          <t>0507-1342-3414</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 208 13층 레이크짐</t>
+          <t>경기도 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lakegym</t>
+          <t>https://blog.naver.com/woongchan_pt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,22 +1067,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dp7g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>287</v>
+        <v>141</v>
       </c>
       <c r="Q7" t="n">
-        <v>500</v>
+        <v>615</v>
       </c>
       <c r="R7" t="n">
-        <v>787</v>
+        <v>756</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1857191169</t>
+          <t>1577544321</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857191169</t>
+          <t>https://m.place.naver.com/place/1577544321</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>뉴짐스PT&amp;크루</t>
+          <t>레이크짐 PT 미사점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>woongchan_pt@naver.com</t>
+          <t>lakegym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1342-3414</t>
+          <t>0507-1469-4114</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
+          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woongchan_pt</t>
+          <t>https://www.instagram.com/lakegym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,22 +1161,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4aasy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="Q8" t="n">
-        <v>615</v>
+        <v>500</v>
       </c>
       <c r="R8" t="n">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1577544321</t>
+          <t>1857191169</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577544321</t>
+          <t>https://m.place.naver.com/place/1857191169</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1263,7 +1235,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
+          <t>경기도 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,7 +1245,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,19 +1255,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46038</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,7 +1427,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기도 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wog61xv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1527,104 +1491,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>jw30-lim@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1345-9570</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/jw30-lim</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4au0e</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>109</v>
-      </c>
-      <c r="R12" t="n">
-        <v>194</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1350773756</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/하남_PT.xlsx
+++ b/naver-place-crawler/results_health/하남_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 미사역점</t>
+          <t>위드짐PT 하남미사</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym43@naver.com</t>
+          <t>withgym01@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1469-2444</t>
+          <t>031-8028-1929</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
+          <t>경기 하남시 미사강변대로 84 305, 306호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym43</t>
+          <t>https://blog.naver.com/withgym01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1494</v>
+        <v>113</v>
       </c>
       <c r="Q2" t="n">
-        <v>1337</v>
+        <v>334</v>
       </c>
       <c r="R2" t="n">
-        <v>2831</v>
+        <v>447</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2037860861</t>
+          <t>1010268294</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037860861</t>
+          <t>https://m.place.naver.com/place/1010268294</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,30 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐맥스 미사역점</t>
+          <t>샤인휘트니스 미사역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gymax_01@naver.com</t>
+          <t>shine_fitness4@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1429-6523</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로84번길 21 남송타워 9층</t>
+          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymax_01</t>
+          <t>https://blog.naver.com/shine_fitness4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -696,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1sjoqj</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -711,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3354</v>
+        <v>901</v>
       </c>
       <c r="Q3" t="n">
-        <v>654</v>
+        <v>2015</v>
       </c>
       <c r="R3" t="n">
-        <v>4008</v>
+        <v>2916</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1328828814</t>
+          <t>1377711586</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328828814</t>
+          <t>https://m.place.naver.com/place/1377711586</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -748,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>더하남 그룹PT 키네틱캠프 미사점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>mvppvm@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>0507-1387-4464</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://blog.naver.com/mvppvm/222632646985</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -790,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48112</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>901</v>
+        <v>753</v>
       </c>
       <c r="Q4" t="n">
-        <v>2015</v>
+        <v>328</v>
       </c>
       <c r="R4" t="n">
-        <v>2916</v>
+        <v>1081</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>1949849359</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/1949849359</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>더하남 그룹PT 키네틱캠프 미사점</t>
+          <t>여성전용 헬스 PT 레이디짐 미사점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mvppvm@naver.com</t>
+          <t>fitgirl24@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1387-4464</t>
+          <t>0507-1345-3449</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+          <t>경기 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mvppvm/222632646985</t>
+          <t>https://blog.naver.com/fitgirl24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -884,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44bi7</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -899,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>753</v>
+        <v>498</v>
       </c>
       <c r="Q5" t="n">
-        <v>328</v>
+        <v>615</v>
       </c>
       <c r="R5" t="n">
-        <v>1081</v>
+        <v>1113</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1949849359</t>
+          <t>1945229916</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949849359</t>
+          <t>https://m.place.naver.com/place/1945229916</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>여성전용 헬스 PT 레이디짐 미사점</t>
+          <t>뉴짐스PT&amp;크루</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitgirl24@naver.com</t>
+          <t>woongchan_pt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1345-3449</t>
+          <t>0507-1342-3414</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
+          <t>경기 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitgirl24</t>
+          <t>https://blog.naver.com/woongchan_pt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -978,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aasy</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>498</v>
+        <v>142</v>
       </c>
       <c r="Q6" t="n">
         <v>615</v>
       </c>
       <c r="R6" t="n">
-        <v>1113</v>
+        <v>757</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1945229916</t>
+          <t>1577544321</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945229916</t>
+          <t>https://m.place.naver.com/place/1577544321</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뉴짐스PT&amp;크루</t>
+          <t>레이크짐 PT 미사점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>woongchan_pt@naver.com</t>
+          <t>lakegym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1342-3414</t>
+          <t>0507-1469-4114</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
+          <t>경기 하남시 미사강변중앙로 208 13층 레이크짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woongchan_pt</t>
+          <t>https://www.instagram.com/lakegym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1067,18 +1087,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dp7g</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="Q7" t="n">
-        <v>615</v>
+        <v>500</v>
       </c>
       <c r="R7" t="n">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1577544321</t>
+          <t>1857191169</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577544321</t>
+          <t>https://m.place.naver.com/place/1857191169</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레이크짐 PT 미사점</t>
+          <t>86피트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lakegym@naver.com</t>
+          <t>86fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1469-4114</t>
+          <t>0507-1300-6180</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
+          <t>경기 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lakegym</t>
+          <t>https://cafe.naver.com/jetleezumba/28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,18 +1185,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46038</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>287</v>
+        <v>431</v>
       </c>
       <c r="Q8" t="n">
-        <v>500</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>787</v>
+        <v>665</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1857191169</t>
+          <t>1987758688</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857191169</t>
+          <t>https://m.place.naver.com/place/1987758688</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1213,39 +1241,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>86피트니스</t>
+          <t>짐맥스 미사역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>86fitness@naver.com</t>
+          <t>gymax_01@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1300-6180</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
+          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jetleezumba/28</t>
+          <t>https://blog.naver.com/gymax_01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1255,15 +1279,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wr0uh6r</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>431</v>
+        <v>3362</v>
       </c>
       <c r="Q9" t="n">
-        <v>234</v>
+        <v>654</v>
       </c>
       <c r="R9" t="n">
-        <v>665</v>
+        <v>4016</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1987758688</t>
+          <t>1328828814</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987758688</t>
+          <t>https://m.place.naver.com/place/1328828814</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1427,7 +1455,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1452,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wog61xv</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,6 +1523,104 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>한걸음 트레이닝센터 하남 미사점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jw30-lim@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1345-9570</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jw30-lim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4au0e</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>109</v>
+      </c>
+      <c r="R12" t="n">
+        <v>194</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1350773756</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1350773756</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/하남_PT.xlsx
+++ b/naver-place-crawler/results_health/하남_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3362</v>
+        <v>3366</v>
       </c>
       <c r="Q2" t="n">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="R2" t="n">
-        <v>4016</v>
+        <v>4023</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -649,34 +649,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>위드짐PT 하남미사</t>
+          <t>베라짐 하남 미사점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>withgym01@naver.com</t>
+          <t>veragym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-8028-1929</t>
+          <t>0507-1343-4012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로 84 305, 306호</t>
+          <t>경기도 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/withgym01</t>
+          <t>https://blog.naver.com/veragym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>113</v>
+        <v>368</v>
       </c>
       <c r="Q3" t="n">
-        <v>334</v>
+        <v>819</v>
       </c>
       <c r="R3" t="n">
-        <v>447</v>
+        <v>1187</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1010268294</t>
+          <t>1870489232</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010268294</t>
+          <t>https://m.place.naver.com/place/1870489232</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -808,10 +808,10 @@
         <v>901</v>
       </c>
       <c r="Q4" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="R4" t="n">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1491,6 +1491,100 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>스포애니 하남시청역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>spoany466@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1415-6681</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신평로 84 동화건설 주차빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany466</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1380</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2380</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>132730406</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/132730406</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/하남_PT.xlsx
+++ b/naver-place-crawler/results_health/하남_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -628,10 +628,10 @@
         <v>368</v>
       </c>
       <c r="Q2" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="R2" t="n">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>위드짐PT 하남미사</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>withgym01@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>031-8028-1929</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기 하남시 미사강변대로 84 305, 306호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://blog.naver.com/withgym01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1sjoqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>914</v>
+        <v>113</v>
       </c>
       <c r="Q3" t="n">
-        <v>2016</v>
+        <v>334</v>
       </c>
       <c r="R3" t="n">
-        <v>2930</v>
+        <v>447</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>1010268294</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/1010268294</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더하남 그룹PT 키네틱캠프 미사점</t>
+          <t>샤인휘트니스 미사역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mvppvm@naver.com</t>
+          <t>shine_fitness4@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1387-4464</t>
+          <t>0507-1429-6523</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mvppvm/222632646985</t>
+          <t>https://blog.naver.com/shine_fitness4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48112</t>
+          <t>https://talk.naver.com/ct/w1sjoqj</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>753</v>
+        <v>914</v>
       </c>
       <c r="Q4" t="n">
-        <v>327</v>
+        <v>2016</v>
       </c>
       <c r="R4" t="n">
-        <v>1080</v>
+        <v>2930</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1949849359</t>
+          <t>1377711586</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949849359</t>
+          <t>https://m.place.naver.com/place/1377711586</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전용 헬스 PT 레이디짐 미사점</t>
+          <t>더하남 그룹PT 키네틱캠프 미사점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitgirl24@naver.com</t>
+          <t>mvppvm@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1345-3449</t>
+          <t>0507-1387-4464</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
+          <t>경기 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitgirl24</t>
+          <t>https://blog.naver.com/mvppvm/222632646985</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44bi7</t>
+          <t>https://talk.naver.com/ct/w48112</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>498</v>
+        <v>753</v>
       </c>
       <c r="Q5" t="n">
-        <v>618</v>
+        <v>327</v>
       </c>
       <c r="R5" t="n">
-        <v>1116</v>
+        <v>1080</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1945229916</t>
+          <t>1949849359</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945229916</t>
+          <t>https://m.place.naver.com/place/1949849359</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프롬더스트릿 하남미사점</t>
+          <t>여성전용 헬스 PT 레이디짐 미사점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fromthestreet@naver.com</t>
+          <t>fitgirl24@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1369-1637</t>
+          <t>0507-1345-3449</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 189 307호</t>
+          <t>경기 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Fromthestreet</t>
+          <t>https://blog.naver.com/fitgirl24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g1gj</t>
+          <t>https://talk.naver.com/ct/w44bi7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>371</v>
+        <v>498</v>
       </c>
       <c r="Q6" t="n">
-        <v>108</v>
+        <v>618</v>
       </c>
       <c r="R6" t="n">
-        <v>479</v>
+        <v>1116</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1280710452</t>
+          <t>1945229916</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1280710452</t>
+          <t>https://m.place.naver.com/place/1945229916</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뉴짐스PT&amp;크루</t>
+          <t>프롬더스트릿 하남미사점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>woongchan_pt@naver.com</t>
+          <t>fromthestreet@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1342-3414</t>
+          <t>0507-1369-1637</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
+          <t>경기 하남시 미사강변중앙로 189 307호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woongchan_pt</t>
+          <t>https://www.youtube.com/@Fromthestreet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4aasy</t>
+          <t>https://talk.naver.com/ct/w4g1gj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>143</v>
+        <v>371</v>
       </c>
       <c r="Q7" t="n">
-        <v>614</v>
+        <v>108</v>
       </c>
       <c r="R7" t="n">
-        <v>757</v>
+        <v>479</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1577544321</t>
+          <t>1280710452</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577544321</t>
+          <t>https://m.place.naver.com/place/1280710452</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,39 +1143,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>카인드짐24시 헬스 PT 미사역점</t>
+          <t>뉴짐스PT&amp;크루</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kindgym8@naver.com</t>
+          <t>woongchan_pt@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1459-2444</t>
+          <t>0507-1342-3414</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변남로 125 미사역 마이움푸르지오시티 B1</t>
+          <t>경기 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_zxeEXK</t>
+          <t>https://blog.naver.com/woongchan_pt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4m5k0</t>
+          <t>https://talk.naver.com/ct/w4aasy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1156</v>
+        <v>143</v>
       </c>
       <c r="Q8" t="n">
-        <v>1328</v>
+        <v>614</v>
       </c>
       <c r="R8" t="n">
-        <v>2484</v>
+        <v>757</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1845162608</t>
+          <t>1577544321</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845162608</t>
+          <t>https://m.place.naver.com/place/1577544321</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1343,39 +1339,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에어바이트 PT 미사점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>airbite@naver.com</t>
-        </is>
-      </c>
+          <t>에이투에프 하남</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1332-4181</t>
+          <t>0507-1381-5791</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기 하남시 대성로319번길 50 한림빌딩 B1호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ko_coach</t>
+          <t>https://a2f.co.kr/trial-reservation.html</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1395,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wog61xv</t>
+          <t>https://talk.naver.com/ct/wo29jot</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1397,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="R10" t="n">
-        <v>105</v>
+        <v>320</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2000579553</t>
+          <t>1744117426</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000579553</t>
+          <t>https://m.place.naver.com/place/1744117426</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스포애니 하남시청역점</t>
+          <t>에어바이트 PT 미사점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>spoany466@naver.com</t>
+          <t>airbite@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-6681</t>
+          <t>0507-1332-4181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 하남시 신평로 84 동화건설 주차빌딩 2층</t>
+          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany466</t>
+          <t>https://www.instagram.com/_ko_coach</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4b7sp</t>
+          <t>https://talk.naver.com/ct/wog61xv</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1385</v>
+        <v>93</v>
       </c>
       <c r="Q11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>2385</v>
+        <v>105</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>132730406</t>
+          <t>2000579553</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/132730406</t>
+          <t>https://m.place.naver.com/place/2000579553</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>jw30-lim@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1345-9570</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/jw30-lim</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4au0e</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>109</v>
-      </c>
-      <c r="R12" t="n">
-        <v>194</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1350773756</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
